--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488279_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488279_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.261200000000001</v>
+        <v>7.655</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4314</v>
+        <v>5.8006</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8297</v>
+        <v>1.8544</v>
       </c>
       <c r="G2" t="n">
         <v>1.5417</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5723</v>
+        <v>-0.0339</v>
       </c>
       <c r="T2" t="n">
-        <v>0.725</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1527</v>
+        <v>-0.1281</v>
       </c>
       <c r="V2" t="n">
         <v>5.0354</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6222</v>
+        <v>5.5717</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9032</v>
+        <v>3.4683</v>
       </c>
       <c r="F3" t="n">
-        <v>2.719</v>
+        <v>2.1034</v>
       </c>
       <c r="G3" t="n">
         <v>2.6486</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1028</v>
+        <v>1.0523</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8344</v>
+        <v>0.3995</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2684</v>
+        <v>0.6528</v>
       </c>
       <c r="V3" t="n">
         <v>0.9444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5895</v>
+        <v>5.4003</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9011</v>
+        <v>3.5641</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6884</v>
+        <v>1.8361</v>
       </c>
       <c r="G4" t="n">
         <v>4.0263</v>
@@ -766,13 +766,13 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0461</v>
+        <v>0.8568</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1043</v>
+        <v>0.7673</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0582</v>
+        <v>0.0895</v>
       </c>
       <c r="V4" t="n">
         <v>1.2583</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7097</v>
+        <v>4.8378</v>
       </c>
       <c r="E5" t="n">
-        <v>2.165</v>
+        <v>2.9484</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5447</v>
+        <v>1.8894</v>
       </c>
       <c r="G5" t="n">
         <v>3.3369</v>
@@ -844,13 +844,13 @@
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2948</v>
+        <v>-0.1666</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4924</v>
+        <v>0.291</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8023</v>
+        <v>-0.4576</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9635</v>
+        <v>3.0647</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5899</v>
+        <v>2.1343</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3736</v>
+        <v>0.9304</v>
       </c>
       <c r="G6" t="n">
         <v>2.2851</v>
@@ -922,13 +922,13 @@
         <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5069</v>
+        <v>-0.4057</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6019</v>
+        <v>-0.0575</v>
       </c>
       <c r="U6" t="n">
-        <v>0.095</v>
+        <v>-0.3482</v>
       </c>
       <c r="V6" t="n">
         <v>0.6294</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0894</v>
+        <v>2.3399</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4328</v>
+        <v>0.6834</v>
       </c>
       <c r="F7" t="n">
         <v>1.6566</v>
@@ -1000,10 +1000,10 @@
         <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7499</v>
+        <v>-0.4993</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4377</v>
+        <v>-0.1871</v>
       </c>
       <c r="U7" t="n">
         <v>-0.3121</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.509</v>
+        <v>1.9806</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7469</v>
+        <v>2.0954</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2379</v>
+        <v>-0.1148</v>
       </c>
       <c r="G8" t="n">
         <v>4.8192</v>
@@ -1078,13 +1078,13 @@
         <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4949</v>
+        <v>-0.0233</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4713</v>
+        <v>-0.1228</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0236</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8888</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3028</v>
+        <v>1.381</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6246</v>
+        <v>-1.3741</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9274</v>
+        <v>2.7551</v>
       </c>
       <c r="G9" t="n">
         <v>0.0086</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0005</v>
+        <v>1.0788</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4514</v>
+        <v>0.702</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5491</v>
+        <v>0.3768</v>
       </c>
       <c r="V9" t="n">
         <v>2.5172</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8065</v>
+        <v>-0.5789</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2271</v>
+        <v>-1.2703</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4206</v>
+        <v>0.6914</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2896</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2024</v>
+        <v>0.0252</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1604</v>
+        <v>0.1172</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3629</v>
+        <v>-0.092</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3144</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6533</v>
+        <v>-1.261</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0813</v>
+        <v>-1.7875</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4279</v>
+        <v>0.5264</v>
       </c>
       <c r="G12" t="n">
         <v>-1.479</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1743</v>
+        <v>0.2179</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1641</v>
+        <v>0.1296</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0102</v>
+        <v>0.0883</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4429</v>
+        <v>-2.5512</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9587</v>
+        <v>-1.8314</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5158</v>
+        <v>-0.7198</v>
       </c>
       <c r="G13" t="n">
-        <v>0.233</v>
+        <v>-0.7068</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3952</v>
+        <v>-1.0985</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6282</v>
+        <v>0.3917</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1853</v>
+        <v>-0.6314</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2067</v>
+        <v>-0.6314</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0214</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4183</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1885</v>
+        <v>-0.4671</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6069</v>
+        <v>0.3917</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1499</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7889</v>
+        <v>-0.6591</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2473</v>
+        <v>-0.2736</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4584</v>
+        <v>-0.3855</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.315</v>
+        <v>-0.6294</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.6551</v>
+        <v>-2.8034</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8861</v>
+        <v>-3.4916</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.769</v>
+        <v>0.6881</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7068</v>
+        <v>0.233</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0985</v>
+        <v>-0.3952</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3917</v>
+        <v>0.6282</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6314</v>
+        <v>-0.1853</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6314</v>
+        <v>-0.2067</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.0214</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.4183</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4671</v>
+        <v>-0.1885</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3917</v>
+        <v>0.6069</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.763</v>
+        <v>0.4284</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3283</v>
+        <v>0.7144</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4347</v>
+        <v>-0.286</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6294</v>
+        <v>-0.315</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>25.1336</v>
+        <v>25.68060000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>11.0366</v>
+        <v>11.5837</v>
       </c>
       <c r="F15" t="n">
-        <v>14.0968</v>
+        <v>14.0967</v>
       </c>
       <c r="G15" t="n">
         <v>19.6665</v>
@@ -1600,7 +1600,7 @@
         <v>14.06250000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>7.8046</v>
+        <v>7.804600000000001</v>
       </c>
       <c r="L15" t="n">
         <v>6.2578</v>
@@ -1624,10 +1624,10 @@
         <v>12.9701</v>
       </c>
       <c r="S15" t="n">
-        <v>1.324399999999999</v>
+        <v>1.8715</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0271</v>
+        <v>2.5742</v>
       </c>
       <c r="U15" t="n">
         <v>-0.7025999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.25</v>
+        <v>2.1125</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0314</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2186</v>
+        <v>1.5708</v>
       </c>
       <c r="G16" t="n">
         <v>1.3469</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>0.144</v>
+        <v>0.0065</v>
       </c>
       <c r="T16" t="n">
-        <v>0.582</v>
+        <v>0.0924</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.438</v>
+        <v>-0.0858</v>
       </c>
       <c r="V16" t="n">
         <v>0.9444</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0548</v>
+        <v>1.3079</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1013</v>
+        <v>0.1992</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9535</v>
+        <v>1.1087</v>
       </c>
       <c r="G17" t="n">
         <v>0.1639</v>
@@ -1780,13 +1780,13 @@
         <v>2.4087</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.053</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.378</v>
+        <v>-0.2801</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.675</v>
+        <v>-0.5198</v>
       </c>
       <c r="V17" t="n">
         <v>1.5733</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0479</v>
+        <v>0.5389</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1506</v>
+        <v>-0.2485</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1985</v>
+        <v>0.7874</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5796</v>
@@ -1858,13 +1858,13 @@
         <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0155</v>
+        <v>0.5064</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3084</v>
+        <v>0.2105</v>
       </c>
       <c r="U18" t="n">
-        <v>0.707</v>
+        <v>0.2959</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.271</v>
+        <v>-1.355</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4015</v>
+        <v>-2.0965</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6725</v>
+        <v>0.7415</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.3128</v>
+        <v>-2.1677</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.82</v>
+        <v>-1.4902</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4928</v>
+        <v>-0.6775</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.7205</v>
+        <v>-1.7098</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1091</v>
+        <v>-0.4254</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.2844</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5922</v>
+        <v>-0.458</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7108</v>
+        <v>-1.0648</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8814</v>
+        <v>0.6069</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R19" t="n">
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8015</v>
+        <v>-0.5409</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7346</v>
+        <v>-0.2014</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0669</v>
+        <v>-0.3395</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3139</v>
+        <v>-0.3139</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8944</v>
+        <v>-1.8433</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4882</v>
+        <v>-1.7363</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5938</v>
+        <v>-0.1071</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1677</v>
+        <v>-1.3804</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4902</v>
+        <v>0.7318</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6775</v>
+        <v>-2.1122</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7098</v>
+        <v>-0.928</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4254</v>
+        <v>1.0306</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2844</v>
+        <v>-1.9586</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.458</v>
+        <v>-0.4524</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0648</v>
+        <v>-0.2989</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6069</v>
+        <v>-0.1536</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0804</v>
+        <v>0.3507</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5931</v>
+        <v>0.1181</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4872</v>
+        <v>0.2325</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3139</v>
+        <v>-0.6283</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3139</v>
+        <v>-0.6283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2104</v>
+        <v>-2.2719</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.128</v>
+        <v>-1.4591</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0824</v>
+        <v>-0.8128</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3804</v>
+        <v>-4.3128</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7318</v>
+        <v>-1.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1122</v>
+        <v>-2.4928</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.928</v>
+        <v>-1.7205</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0306</v>
+        <v>-1.1091</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9586</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4524</v>
+        <v>-2.5922</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2989</v>
+        <v>-0.7108</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1536</v>
+        <v>-1.8814</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7411</v>
+        <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0164</v>
+        <v>0.8005</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2736</v>
+        <v>0.8739</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2572</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6283</v>
+        <v>0.3139</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3139</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.351</v>
+        <v>-2.7543</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5932</v>
+        <v>-1.2994</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7578</v>
+        <v>-1.4548</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9587</v>
@@ -2170,13 +2170,13 @@
         <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.207</v>
+        <v>-0.6103</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.475</v>
+        <v>-0.1812</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.732</v>
+        <v>-0.429</v>
       </c>
       <c r="V22" t="n">
         <v>1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7319</v>
+        <v>-3.6821</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0769</v>
+        <v>-1.1748</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6551</v>
+        <v>-2.5073</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2143</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2969</v>
+        <v>-0.2471</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1256</v>
+        <v>-0.2235</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1714</v>
+        <v>-0.0236</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5177</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6713</v>
+        <v>-4.0339</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4622</v>
+        <v>-3.9726</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2091</v>
+        <v>-0.0613</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1077</v>
@@ -2326,13 +2326,13 @@
         <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0257</v>
+        <v>-0.3883</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.526</v>
+        <v>-0.0364</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4997</v>
+        <v>-0.3519</v>
       </c>
       <c r="V24" t="n">
         <v>0.315</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9715</v>
+        <v>-5.6039</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0764</v>
+        <v>0.2174</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.8951</v>
+        <v>-5.8213</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1779</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1127</v>
+        <v>0.4803</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0037</v>
+        <v>0.2901</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1164</v>
+        <v>0.1903</v>
       </c>
       <c r="V25" t="n">
         <v>-4.721</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.3847</v>
+        <v>-6.8956</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6556</v>
+        <v>-3.068</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.7291</v>
+        <v>-3.8275</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2781</v>
@@ -2482,13 +2482,13 @@
         <v>0.3706</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7185</v>
+        <v>-0.2294</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5471</v>
+        <v>0.0404</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1714</v>
+        <v>-0.2699</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8321</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-25.1335</v>
+        <v>-24.4807</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.0969</v>
+        <v>-14.0968</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.0367</v>
+        <v>-10.3837</v>
       </c>
       <c r="G27" t="n">
         <v>-19.6664</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.3079</v>
+        <v>-3.307900000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-16.3587</v>
@@ -2536,7 +2536,7 @@
         <v>-5.603899999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4969</v>
+        <v>4.496900000000001</v>
       </c>
       <c r="L27" t="n">
         <v>-10.1008</v>
@@ -2545,13 +2545,13 @@
         <v>-14.0624</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.804600000000001</v>
+        <v>-7.8046</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.2576</v>
+        <v>-6.257600000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>2.779200000000001</v>
+        <v>2.7792</v>
       </c>
       <c r="Q27" t="n">
         <v>-12.97</v>
@@ -2560,13 +2560,13 @@
         <v>15.7494</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.324199999999999</v>
+        <v>-0.6715000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7028999999999997</v>
+        <v>0.7027999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.0272</v>
+        <v>-1.3742</v>
       </c>
       <c r="V27" t="n">
         <v>-6.921900000000001</v>
